--- a/flowhq-outreach/templates/FlowHQ-Outreach-Template.xlsx
+++ b/flowhq-outreach/templates/FlowHQ-Outreach-Template.xlsx
@@ -1307,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1476,32 +1476,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RESEARCH_BATCH_SIZE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SEND_LOCK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leads researched per run.</t>
+          <t>Managed by workflow 04: holds "&lt;run&gt;|&lt;time&gt;" while a send run is in progress so overlapping runs cannot work the same queue. Expires after 30 minutes. Leave empty.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>RESEARCH_BATCH_SIZE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Leads researched per run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>GENERATION_BATCH_SIZE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Drafts generated per run.</t>
         </is>
